--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capital Bank, N.A.</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a14f0a465bfe84f</t>
+          <t>https://www.indeed.com/viewjob?jk=402d9ccd9278b80f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analyst, Information Technology (Data Engineer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oriental Bank</t>
+          <t>Capital Bank, N.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=4a14f0a465bfe84f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Analyst, Information Technology (Data Engineer)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>Oriental Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Linux CloudSystem Engineer</t>
+          <t>Data Engineer &amp; Database Administrator II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnologix Limited</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Linux CloudSystem Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Tecnologix Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer- Remote US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RH Digital Strategy and Merchandising</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corte Madera, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Azure, BigQuery, Spark, Oracle</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ff12aace30b55c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Industrial Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Esi solutions</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sisters, OR, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Industrial Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Esi solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sisters, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agentic AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr IT Architect- Database</t>
+          <t>Agentic AI Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEODIS</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Java and Python Full Stack Developer</t>
+          <t>Sr IT Architect- Database</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>GEODIS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4112e7da8d56fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Java and Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4112e7da8d56fc7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>ServiceNow Business Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CCM Consulting Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ef6bd764aed2ae</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zerto Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>www.prolim.com</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af0c39069689ff0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Zerto Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>www.prolim.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3af0c39069689ff0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,89 +1546,89 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Test Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3a1279fc588cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,147 +1781,147 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Applications Architect (Global Security Class Actions)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Kafka, Kafka Connect, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b2937ebe949351</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae7bf11c539daa6</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,94 +1931,94 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619f0f0e3a4ac4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d0de22265232e</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71cabdc237f48ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Java Backend Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1e5da7a2f01fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae7bf11c539daa6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=619f0f0e3a4ac4a0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d0de22265232e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tableau Developer- Remote</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=71cabdc237f48ac7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Java Backend Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1e5da7a2f01fe0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>2U</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, dbt, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+          <t>https://www.indeed.com/viewjob?jk=e072650f295cc478</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer-Infrastructure</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0aa97856927508a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb73301c658fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>API Automation</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Potawatomi Federal Solutions</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4068381ee6ee32a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Command Cyber Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,15 +2586,400 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Software Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tractor Zoom, Inc.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sr. Software Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Applied Information Sciences</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b412ebc606edfd11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INTRAFI</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0aa97856927508a</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ETL, ELT, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fbb73301c658fc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>API Automation</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Potawatomi Federal Solutions</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4068381ee6ee32a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Command Cyber Solutions</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a6829c961c144999</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fdd121cf76131f</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Agentic AI Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agentic AI Data Engineer</t>
+          <t>Sr IT Architect- Database</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>GEODIS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr IT Architect- Database</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEODIS</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Java and Python Full Stack Developer</t>
+          <t>ServiceNow Business Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>CCM Consulting Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4112e7da8d56fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ef6bd764aed2ae</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ServiceNow Business Analyst</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CCM Consulting Services</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ef6bd764aed2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zerto Architect</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>www.prolim.com</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af0c39069689ff0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcb8527a918f423</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,104 +1641,104 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Applications Architect (Global Security Class Actions)</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Kafka Connect, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b2937ebe949351</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,129 +1896,129 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae7bf11c539daa6</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619f0f0e3a4ac4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d0de22265232e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71cabdc237f48ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Java Backend Developer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1e5da7a2f01fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2U</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, dbt, Python</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e072650f295cc478</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Salesforce Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Tractor Zoom, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>API Automation</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tableau Developer- Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,472 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Software Engineer-Infrastructure</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior CloudOps Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Alexandria, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Software Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tractor Zoom, Inc.</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Sr. Software Architect</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Applied Information Sciences</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b412ebc606edfd11</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>INTRAFI</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0aa97856927508a</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ETL, ELT, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb73301c658fc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>API Automation</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Potawatomi Federal Solutions</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4068381ee6ee32a7</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Command Cyber Solutions</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6829c961c144999</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>senior Salesforce Administrator &amp; Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>Navar Security</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=80d5bcdaa4e911a8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ServiceNow Business Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CCM Consulting Services</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ef6bd764aed2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ServiceNow Business Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>CCM Consulting Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ef6bd764aed2ae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,64 +1116,64 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, BigQuery, Hadoop, Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb42007cbd45836e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcb8527a918f423</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcb8527a918f423</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,94 +1721,94 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,129 +1966,129 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>JustPaid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=27aacac9d59c4cf3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tableau Developer- Remote</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,182 +2201,182 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>API Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,15 +2516,260 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Software Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tractor Zoom, Inc.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>API Automation</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Industrial Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Esi solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Sisters, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
+          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Industrial Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Esi solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sisters, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcb8527a918f423</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Tractor Zoom, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
+          <t>API Automation</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>API Automation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,15 +2761,50 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Linux CloudSystem Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tecnologix Limited</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer- Remote US</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Industrial Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Esi solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Sisters, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
+          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Industrial Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Esi solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sisters, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr IT Architect- Database</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEODIS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Agentic AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr IT Architect- Database</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEODIS</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>senior Salesforce Administrator &amp; Developer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navar Security</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d5bcdaa4e911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ServiceNow Business Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CCM Consulting Services</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ef6bd764aed2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
@@ -1313,20 +1313,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,129 +1406,129 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb42007cbd45836e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,147 +1536,147 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,94 +1686,94 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>JD - Senior Software Engineer 1, ML</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,129 +1966,129 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JustPaid</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27aacac9d59c4cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,94 +2386,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Salesforce Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Tractor Zoom, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tableau Developer- Remote</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>Kinesis, Databricks, BigQuery, Hive, Spark, Scala, Kafka, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f778e82eb9d3a8f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,190 +2621,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>API Automation</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,122 +503,122 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer &amp; Database Administrator II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital Bank, N.A.</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a14f0a465bfe84f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analyst, Information Technology (Data Engineer)</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oriental Bank</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer- Remote US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr IT Architect- Database</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEODIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr IT Architect- Database</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEODIS</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,69 +1501,69 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,42 +1826,42 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tableau Developer- Remote</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ABCO COMPUTERS PVT LTD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>Senior Salesforce Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Tractor Zoom, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>Kinesis, Databricks, BigQuery, Hive, Spark, Scala, Kafka, Snowflake, MySQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=f778e82eb9d3a8f1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Hive, Spark, Scala, Kafka, Snowflake, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f778e82eb9d3a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
         </is>
       </c>
     </row>
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,85 +2551,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Specialist</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,200 +468,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer - Platform Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>IntegriChain</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>31.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Kinesis, Redshift, Timestream, Step Functions, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402d9ccd9278b80f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2a75955286c43d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator II</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>PGW Auto Glass</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3d77615dc2cb49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
+          <t>https://www.indeed.com/viewjob?jk=402d9ccd9278b80f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer &amp; Database Administrator II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer- Remote US</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JD - Senior Software Engineer 1, ML</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, ELT, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Product Engineer, Alternatives</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,186 +2232,186 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>JD - Senior Software Engineer 1, ML</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Hive, Spark, Scala, Kafka, Snowflake, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f778e82eb9d3a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,75 +2491,495 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Consultant, Cloud Solutions</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Burwood Group</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ABCO COMPUTERS PVT LTD</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tractor Zoom, Inc.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Specialist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>via</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>ETL/Data Integration Developer (Remote Opportunity)</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D73" t="n">
         <v>10.4</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator II</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,89 +636,89 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer &amp; Database Administrator II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Industrial Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Esi solutions</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sisters, OR, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr IT Architect- Database</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEODIS</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,49 +846,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,50 +898,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Paramus, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,77 +986,77 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Corporate Treasury, Payments Platform, Software Engineering, Associate, NY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f52b1b3f85fbccca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Corporate Treasury, Payments Platform, Software Engineering, Associate, Dallas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=721e3da7a4ed9569</t>
         </is>
       </c>
     </row>
@@ -1068,195 +1068,195 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,42 +1371,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
@@ -1418,20 +1418,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,54 +1511,54 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,112 +1641,112 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior DevOps Engineer- Arlington, VA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=896ef6d5605394c3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Product Engineer, Alternatives</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JD - Senior Software Engineer 1, ML</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, ELT, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Product Engineer, Alternatives</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, SQS, ECS, RDS, GCP, Kafka, NoSQL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>JD - Senior Software Engineer 1, ML</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>People Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,40 +2946,600 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Technical Product Owner II</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Computer Services Inc.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer (L2) Segment Team</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Consultant, Cloud Solutions</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Burwood Group</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AWS Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ABCO COMPUTERS PVT LTD</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ocrolus</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, Docker, Kubernetes, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c6ab699a2979fd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Principle Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Databricks Architect</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Onebridge</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tractor Zoom, Inc.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Specialist</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>via</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>ETL/Data Integration Developer (Remote Opportunity)</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D89" t="n">
         <v>10.4</v>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Massachusetts Bay Transportation Authority</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer- Arlington, VA</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896ef6d5605394c3</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior DevOps Engineer- Arlington, VA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=896ef6d5605394c3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Product Engineer, Alternatives</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf8b3db022a654</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Product Engineer, Alternatives</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,69 +2551,69 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, GCP, Kafka, NoSQL, Splunk, CI/CD, Terraform</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JD - Senior Software Engineer 1, ML</t>
+          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>People Inc.</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, ELT, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, GCP, Kafka, NoSQL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d672ede61ebda4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Senior Software Engineer in Test, AI Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e62745232963aca</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Salesforce Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Tractor Zoom, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
         </is>
       </c>
     </row>
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,15 +3531,50 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
         </is>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Databricks Architect (Enterprise Data Platform) ___ Princeton, NJ Hybrid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>MomentoUSA LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=c433cd5dea6cc90b</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator II</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Data Engineer &amp; Database Administrator II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
         </is>
       </c>
     </row>
@@ -818,35 +818,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paramus, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Spark Streaming, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e8742b70400327</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Massachusetts Bay Transportation Authority</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb6b1cb249a4e48</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,69 +1711,69 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Icario</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
         </is>
       </c>
     </row>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
+          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Product Engineer, Alternatives</t>
+          <t>Senior Applications Architect (Global Security Class Actions)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Edgewood, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Kafka Connect, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b2937ebe949351</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Product Engineer, Alternatives</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Senior Advisor - Evernorth</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,69 +2586,69 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, GCP, Kafka, NoSQL, Splunk, CI/CD, Terraform</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
+          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JustPaid</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=27aacac9d59c4cf3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae7bf11c539daa6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=619f0f0e3a4ac4a0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=e72d0de22265232e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II, Lennar.com</t>
+          <t>Senior Agentic (AI) Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
+          <t>https://www.indeed.com/viewjob?jk=71cabdc237f48ac7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Senior Java Backend Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1e5da7a2f01fe0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Odyssey Logistics &amp; Technology Corporation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, MLflow, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f121937478b6b39d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, SQS, ECS, RDS, GCP, Kafka, NoSQL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,89 +3121,89 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ABCO COMPUTERS PVT LTD</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,29 +3251,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Step Functions, S3, SNS, ECS, RDS, REST API integration</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45c5999f784ebb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ocrolus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6ab699a2979fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer in Test, AI Engineering</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e62745232963aca</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Ocrolus</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6ab699a2979fd4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+          <t>Architect, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Little Caesars Pizza</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,332 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c5d9b0760a2bcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tractor Zoom, Inc.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr. Software Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Applied Information Sciences</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b412ebc606edfd11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>INTRAFI</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0aa97856927508a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Databricks Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Onebridge</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer in Test, AI Engineering</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TWG Global AI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e62745232963aca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Specialist</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>via</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-15.xlsx
+++ b/results/job_matches_2026-05-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Architect (Enterprise Data Platform) ___ Princeton, NJ Hybrid</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MomentoUSA LLC</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Photon, GCP</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c433cd5dea6cc90b</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer &amp; Database Administrator II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>3MD Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,77 +696,77 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator II</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
+          <t>https://www.indeed.com/viewjob?jk=894b0939d20a58ea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf3370540eacedd</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,52 +871,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb55025a2943526</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Corporate Treasury, Payments Platform, Software Engineering, Associate, NY</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52b1b3f85fbccca</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Corporate Treasury, Payments Platform, Software Engineering, Associate, Dallas</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721e3da7a4ed9569</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Scala, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59084da1c754fd35</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c44b7e0d27a573e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=5dde1fd2f7b5d9f9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25febc74557100c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Icario</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Dataflow, Scala, MySQL, Talend, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818357b4eb0b5728</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer- Arlington, VA</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896ef6d5605394c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf8b3db022a654</t>
+          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Applications Architect (Global Security Class Actions)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Edgewood, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Kafka Connect, NoSQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b2937ebe949351</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Product Engineer, Alternatives</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ELT, DataOps, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85493af98c332665</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,94 +2561,94 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisor - Evernorth</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8100b86ba469b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Proscia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d421b80978ac8e41</t>
+          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JustPaid</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27aacac9d59c4cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae7bf11c539daa6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619f0f0e3a4ac4a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72d0de22265232e</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Agentic (AI) Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Kafka, PostgreSQL, MLOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71cabdc237f48ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Java Backend Developer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1e5da7a2f01fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Odyssey Logistics &amp; Technology Corporation</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, MLflow, Python</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f121937478b6b39d</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Asset Protection (Hybrid - Seattle)</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, GCP, Kafka, NoSQL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea5cc14aef02ebc</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,172 +3051,172 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Cloud Services Database Specialist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Centric Software</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=f68db530cad44d37</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Salesforce Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tractor Zoom, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3461,437 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Ocrolus</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, Docker, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6ab699a2979fd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Principle Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Paradigm</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Architect, Data &amp; Analytics Engineering</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Little Caesars Pizza</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5d9b0760a2bcaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Tractor Zoom, Inc.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>West Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Software Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Applied Information Sciences</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b412ebc606edfd11</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>INTRAFI</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0aa97856927508a</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c347401a04ad4</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Onebridge</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>ETL/Data Integration Developer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7c4088dcd3b0bdf1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer in Test, AI Engineering</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TWG Global AI</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e62745232963aca</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Specialist</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>via</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
